--- a/Unity/Assets/Config/Excel/RechargeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21840" windowHeight="11115"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +44,9 @@
     <t>RewardItem</t>
   </si>
   <si>
+    <t>Point</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -63,6 +66,9 @@
   </si>
   <si>
     <t>道具</t>
+  </si>
+  <si>
+    <t>积分</t>
   </si>
   <si>
     <t>2;60</t>
@@ -1137,17 +1143,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="3"/>
     <col min="3" max="4" width="20.625" style="3" customWidth="1"/>
     <col min="5" max="5" width="43.125" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="17.875" style="3"/>
+    <col min="6" max="6" width="20.625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1163,42 +1170,51 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1209,10 +1225,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="F4" s="2">
+        <v>60</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1223,10 +1242,13 @@
         <v>30</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F5" s="2">
+        <v>300</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1237,10 +1259,13 @@
         <v>50</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="F6" s="2">
+        <v>500</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1251,10 +1276,13 @@
         <v>98</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F7" s="2">
+        <v>980</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1265,10 +1293,13 @@
         <v>198</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1980</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1279,10 +1310,13 @@
         <v>298</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2980</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1293,10 +1327,13 @@
         <v>488</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4880</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:5">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:6">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1307,7 +1344,10 @@
         <v>648</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6480</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/RechargeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Price</t>
   </si>
   <si>
-    <t>RewardItem</t>
+    <t>Diamond</t>
   </si>
   <si>
     <t>Point</t>
@@ -53,9 +53,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>(array#sep=@),rewardItem</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -65,34 +62,34 @@
     <t>价格</t>
   </si>
   <si>
-    <t>道具</t>
+    <t>钻石</t>
   </si>
   <si>
     <t>积分</t>
   </si>
   <si>
-    <t>2;60</t>
-  </si>
-  <si>
-    <t>2;300</t>
-  </si>
-  <si>
-    <t>2;500</t>
-  </si>
-  <si>
-    <t>2;9800</t>
-  </si>
-  <si>
-    <t>2;19800</t>
-  </si>
-  <si>
-    <t>2;29800</t>
-  </si>
-  <si>
-    <t>2;48800</t>
-  </si>
-  <si>
-    <t>2;64800</t>
+    <t>60</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>9800</t>
+  </si>
+  <si>
+    <t>19800</t>
+  </si>
+  <si>
+    <t>29800</t>
+  </si>
+  <si>
+    <t>48800</t>
+  </si>
+  <si>
+    <t>64800</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1146,7 @@
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="3"/>
     <col min="3" max="4" width="20.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="43.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="28.375" style="4" customWidth="1"/>
     <col min="6" max="6" width="20.625" style="3" customWidth="1"/>
     <col min="7" max="16384" width="17.875" style="3"/>
   </cols>
@@ -1188,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>7</v>
@@ -1196,22 +1193,22 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="2:6">
@@ -1225,7 +1222,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2">
         <v>60</v>
@@ -1242,7 +1239,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2">
         <v>300</v>
@@ -1259,7 +1256,7 @@
         <v>50</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2">
         <v>500</v>
@@ -1276,7 +1273,7 @@
         <v>98</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2">
         <v>980</v>
@@ -1293,7 +1290,7 @@
         <v>198</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2">
         <v>1980</v>
@@ -1310,7 +1307,7 @@
         <v>298</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2">
         <v>2980</v>
@@ -1327,7 +1324,7 @@
         <v>488</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2">
         <v>4880</v>
@@ -1344,7 +1341,7 @@
         <v>648</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2">
         <v>6480</v>

--- a/Unity/Assets/Config/Excel/RechargeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -74,22 +74,16 @@
     <t>300</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
     <t>9800</t>
   </si>
   <si>
+    <t>1280</t>
+  </si>
+  <si>
     <t>19800</t>
   </si>
   <si>
-    <t>29800</t>
-  </si>
-  <si>
-    <t>48800</t>
-  </si>
-  <si>
-    <t>64800</t>
+    <t>32800</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1253,13 +1247,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="2">
-        <v>500</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="2:6">
@@ -1270,13 +1264,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2">
-        <v>980</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="2:6">
@@ -1304,47 +1298,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2">
-        <v>2980</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:6">
-      <c r="B10" s="2">
-        <v>10000007</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>488</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4880</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:6">
-      <c r="B11" s="2">
-        <v>10000008</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>648</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2">
-        <v>6480</v>
+        <v>3280</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/RechargeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9555"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Diamond</t>
   </si>
   <si>
-    <t>Point</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
   </si>
   <si>
     <t>钻石</t>
-  </si>
-  <si>
-    <t>积分</t>
   </si>
   <si>
     <t>60</t>
@@ -1134,18 +1128,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="3"/>
     <col min="3" max="4" width="20.625" style="3" customWidth="1"/>
     <col min="5" max="5" width="28.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.875" style="3" customWidth="1"/>
     <col min="7" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,51 +1155,42 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1216,13 +1201,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1233,13 +1215,10 @@
         <v>30</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2">
-        <v>300</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1250,13 +1229,10 @@
         <v>98</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2">
-        <v>980</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1267,13 +1243,10 @@
         <v>128</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1280</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1284,13 +1257,10 @@
         <v>198</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1980</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:6">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:5">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1301,10 +1271,7 @@
         <v>328</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3280</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
